--- a/data/trans_bre/IP13-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP13-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,36</t>
+          <t>3,05</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>102,32%</t>
+          <t>127,88%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 10,95</t>
+          <t>-2,48; 10,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,76; 5,41</t>
+          <t>-13,92; 4,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,7; -0,91</t>
+          <t>-15,13; -0,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 7,98</t>
+          <t>-2,59; 8,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-67,77; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-81,46; 98,54</t>
+          <t>-80,71; 90,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 29,74</t>
+          <t>-100,0; 74,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-82,22; —</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-2,5</t>
+          <t>-1,33</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-38,13%</t>
+          <t>-20,7%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 5,34</t>
+          <t>-5,42; 5,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,09; 4,06</t>
+          <t>-8,58; 4,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 11,16</t>
+          <t>-2,23; 10,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 2,2</t>
+          <t>-6,69; 4,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-58,91; 151,23</t>
+          <t>-61,58; 144,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-61,27; 53,89</t>
+          <t>-58,4; 61,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-16,55; 323,21</t>
+          <t>-31,74; 273,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-83,29; 56,47</t>
+          <t>-75,01; 119,09</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,4</t>
+          <t>1,61</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>30,28%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 4,91</t>
+          <t>-3,16; 5,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 6,89</t>
+          <t>-8,3; 6,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 5,31</t>
+          <t>-1,95; 5,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 8,69</t>
+          <t>-5,75; 8,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-71,09; 190,29</t>
+          <t>-71,99; 158,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-71,85; 447,74</t>
+          <t>-74,49; 385,34</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,65</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,57%</t>
         </is>
       </c>
     </row>
@@ -960,37 +960,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,35; 2,17</t>
+          <t>-10,27; 2,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 4,09</t>
+          <t>-7,19; 3,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 2,72</t>
+          <t>-10,39; 1,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 5,48</t>
+          <t>-4,79; 6,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-85,38; 80,92</t>
+          <t>-86,92; 85,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 325,96</t>
+          <t>-90,1; 253,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-88,51; 109,35</t>
+          <t>-92,34; 77,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,43</t>
+          <t>-2,04</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-16,36%</t>
+          <t>-21,91%</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 8,2</t>
+          <t>-2,74; 8,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 13,8</t>
+          <t>-7,29; 13,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 13,12</t>
+          <t>-3,29; 14,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 7,66</t>
+          <t>-12,69; 7,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,17 +1085,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-59,68; 449,71</t>
+          <t>-65,77; 422,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-66,56; 897,46</t>
+          <t>-61,89; 807,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-82,22; 191,79</t>
+          <t>-82,34; 212,4</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,51</t>
+          <t>2,03</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>32,62%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 6,39</t>
+          <t>-3,34; 6,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 5,9</t>
+          <t>-3,46; 6,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 2,39</t>
+          <t>-5,76; 2,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 10,18</t>
+          <t>-5,94; 10,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-63,33; 448,74</t>
+          <t>-72,6; 339,74</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1,21</t>
+          <t>-1,6</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-11,66%</t>
+          <t>-14,46%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 6,35</t>
+          <t>-1,34; 6,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 4,97</t>
+          <t>-1,69; 4,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 3,93</t>
+          <t>-1,78; 3,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 5,65</t>
+          <t>-7,87; 5,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-41,3; 630,78</t>
+          <t>-46,96; 654,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-71,19; 630,11</t>
+          <t>-63,73; 555,4</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-76,58; 560,75</t>
+          <t>-68,92; 525,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-54,14; 78,79</t>
+          <t>-56,48; 68,5</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-2,11</t>
+          <t>-2,76</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-37,12%</t>
+          <t>-48,63%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-8,71; -0,04</t>
+          <t>-8,61; -0,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 2,55</t>
+          <t>-4,37; 2,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 6,63</t>
+          <t>-0,99; 7,18</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 1,28</t>
+          <t>-6,73; 0,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-76,4; 0,35</t>
+          <t>-78,53; -0,31</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-69,94; 106,89</t>
+          <t>-69,18; 118,91</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-19,49; 229,5</t>
+          <t>-19,73; 288,15</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-77,89; 44,4</t>
+          <t>-82,12; 34,27</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0,73</t>
+          <t>-0,67</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-11,53%</t>
+          <t>-10,25%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 1,5</t>
+          <t>-2,21; 1,39</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 1,51</t>
+          <t>-2,57; 1,56</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 2,77</t>
+          <t>-0,82; 2,67</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 1,56</t>
+          <t>-2,79; 1,56</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-37,17; 36,7</t>
+          <t>-38,22; 31,18</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-37,72; 29,79</t>
+          <t>-36,97; 31,39</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-17,81; 78,47</t>
+          <t>-17,21; 74,36</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-40,14; 29,18</t>
+          <t>-36,81; 32,0</t>
         </is>
       </c>
     </row>
